--- a/app/src/main/assets/methodmesh/odk_templates/qrcode/example_odk_showcase_barcode_scan.xlsx
+++ b/app/src/main/assets/methodmesh/odk_templates/qrcode/example_odk_showcase_barcode_scan.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Rf879ecd078ab40c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rb45c6359113b4fbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R93223902af4d4902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R4a74f05d38af474f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R6a645e07e0f04403"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rb52e01c9cf764380"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -334,17 +334,17 @@
         <x:v>MethodMesh Automatic code scanner — barcode.scan</x:v>
       </x:c>
       <x:c r="D2" s="8" t="str">
-        <x:v>Capture a QR token as verifiable workflow evidence</x:v>
-      </x:c>
-      <x:c r="E2" s="8" t="str"/>
-      <x:c r="F2" s="8" t="str"/>
-      <x:c r="G2" s="8" t="str"/>
-      <x:c r="H2" s="8" t="str"/>
-      <x:c r="I2" s="8" t="str"/>
-      <x:c r="J2" s="8" t="str"/>
-      <x:c r="K2" s="8" t="str"/>
-      <x:c r="L2" s="8" t="str"/>
-      <x:c r="M2" s="8" t="str"/>
+        <x:v>Scan a QR, Data Matrix, Aztec, PDF417 or common 1D barcode with MethodMesh. The scan is performed in the native scanner and returned only after Commit.</x:v>
+      </x:c>
+      <x:c r="E2" s="8"/>
+      <x:c r="F2" s="8"/>
+      <x:c r="G2" s="8"/>
+      <x:c r="H2" s="8"/>
+      <x:c r="I2" s="8"/>
+      <x:c r="J2" s="8"/>
+      <x:c r="K2" s="8"/>
+      <x:c r="L2" s="8"/>
+      <x:c r="M2" s="8"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="8" t="str">
@@ -357,20 +357,20 @@
         <x:v>Run barcode.scan</x:v>
       </x:c>
       <x:c r="D3" s="8" t="str">
-        <x:v>This form invokes only this MethodMesh capability. Inputs shown here are only those relevant to this call; capability interaction may continue in the native MethodMesh surface and return on Commit.</x:v>
+        <x:v>One MethodMesh capability invocation. Canonical return fields are unprefixed and the shared metadata payload is captured in methodmesh_full_json.</x:v>
       </x:c>
       <x:c r="E3" s="8" t="str">
         <x:v>field-list</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str"/>
-      <x:c r="G3" s="8" t="str"/>
-      <x:c r="H3" s="8" t="str"/>
-      <x:c r="I3" s="8" t="str"/>
-      <x:c r="J3" s="8" t="str"/>
-      <x:c r="K3" s="8" t="str"/>
-      <x:c r="L3" s="8" t="str"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+      <x:c r="H3" s="8"/>
+      <x:c r="I3" s="8"/>
+      <x:c r="J3" s="8"/>
+      <x:c r="K3" s="8"/>
+      <x:c r="L3" s="8"/>
       <x:c r="M3" s="8" t="str">
-        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='barcode.scan',input_barcode_formats=${barcode_formats_input},input_payload_mode='FULL',methodmesh_return_namespace='scan',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='barcode.scan',input_barcode_formats=${barcode_formats_input},input_payload_mode='FULL',return_mode='flat')</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -383,16 +383,18 @@
       <x:c r="C4" s="8" t="str">
         <x:v>Accepted code formats (optional)</x:v>
       </x:c>
-      <x:c r="D4" s="8" t="str"/>
-      <x:c r="E4" s="8" t="str"/>
-      <x:c r="F4" s="8" t="str"/>
-      <x:c r="G4" s="8" t="str"/>
-      <x:c r="H4" s="8" t="str"/>
-      <x:c r="I4" s="8" t="str"/>
-      <x:c r="J4" s="8" t="str"/>
-      <x:c r="K4" s="8" t="str"/>
-      <x:c r="L4" s="8" t="str"/>
-      <x:c r="M4" s="8" t="str"/>
+      <x:c r="D4" s="8" t="str">
+        <x:v>Leave blank for automatic detection of all supported formats.</x:v>
+      </x:c>
+      <x:c r="E4" s="8"/>
+      <x:c r="F4" s="8"/>
+      <x:c r="G4" s="8"/>
+      <x:c r="H4" s="8"/>
+      <x:c r="I4" s="8"/>
+      <x:c r="J4" s="8"/>
+      <x:c r="K4" s="8"/>
+      <x:c r="L4" s="8"/>
+      <x:c r="M4" s="8"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="8" t="str">
@@ -402,415 +404,377 @@
         <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
-        <x:v>Methodmesh Status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D5" s="8" t="str">
-        <x:v>Shared MethodMesh transport status, where projected by the runtime.</x:v>
+        <x:v>Shared MethodMesh transport status.</x:v>
       </x:c>
       <x:c r="E5" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F5" s="8" t="str"/>
-      <x:c r="G5" s="8" t="str"/>
-      <x:c r="H5" s="8" t="str"/>
-      <x:c r="I5" s="8" t="str"/>
-      <x:c r="J5" s="8" t="str"/>
-      <x:c r="K5" s="8" t="str"/>
+      <x:c r="F5" s="8"/>
+      <x:c r="G5" s="8"/>
+      <x:c r="H5" s="8"/>
+      <x:c r="I5" s="8"/>
+      <x:c r="J5" s="8"/>
+      <x:c r="K5" s="8"/>
       <x:c r="L5" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M5" s="8" t="str"/>
+      <x:c r="M5" s="8"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
-        <x:v>scan_methodmesh_execution_id</x:v>
+        <x:v>barcode_payload</x:v>
       </x:c>
       <x:c r="C6" s="8" t="str">
-        <x:v>MethodMesh execution ID</x:v>
+        <x:v>Decoded payload</x:v>
       </x:c>
       <x:c r="D6" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Primary barcode.scan result.</x:v>
       </x:c>
       <x:c r="E6" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="str"/>
-      <x:c r="G6" s="8" t="str"/>
-      <x:c r="H6" s="8" t="str"/>
-      <x:c r="I6" s="8" t="str"/>
-      <x:c r="J6" s="8" t="str"/>
-      <x:c r="K6" s="8" t="str"/>
+      <x:c r="F6" s="8"/>
+      <x:c r="G6" s="8"/>
+      <x:c r="H6" s="8"/>
+      <x:c r="I6" s="8"/>
+      <x:c r="J6" s="8"/>
+      <x:c r="K6" s="8"/>
       <x:c r="L6" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M6" s="8" t="str"/>
+      <x:c r="M6" s="8"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
-        <x:v>scan_methodmesh_status</x:v>
+        <x:v>barcode_format</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
-        <x:v>MethodMesh status</x:v>
+        <x:v>Detected barcode format</x:v>
       </x:c>
       <x:c r="D7" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Canonical barcode format name.</x:v>
       </x:c>
       <x:c r="E7" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="str"/>
-      <x:c r="G7" s="8" t="str"/>
-      <x:c r="H7" s="8" t="str"/>
-      <x:c r="I7" s="8" t="str"/>
-      <x:c r="J7" s="8" t="str"/>
-      <x:c r="K7" s="8" t="str"/>
+      <x:c r="F7" s="8"/>
+      <x:c r="G7" s="8"/>
+      <x:c r="H7" s="8"/>
+      <x:c r="I7" s="8"/>
+      <x:c r="J7" s="8"/>
+      <x:c r="K7" s="8"/>
       <x:c r="L7" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M7" s="8" t="str"/>
+      <x:c r="M7" s="8"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
-        <x:v>scan_barcode_payload</x:v>
+        <x:v>barcode_payload_kind</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
-        <x:v>Decoded payload</x:v>
+        <x:v>Payload type</x:v>
       </x:c>
       <x:c r="D8" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>text or url.</x:v>
       </x:c>
       <x:c r="E8" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="str"/>
-      <x:c r="G8" s="8" t="str"/>
-      <x:c r="H8" s="8" t="str"/>
-      <x:c r="I8" s="8" t="str"/>
-      <x:c r="J8" s="8" t="str"/>
-      <x:c r="K8" s="8" t="str"/>
+      <x:c r="F8" s="8"/>
+      <x:c r="G8" s="8"/>
+      <x:c r="H8" s="8"/>
+      <x:c r="I8" s="8"/>
+      <x:c r="J8" s="8"/>
+      <x:c r="K8" s="8"/>
       <x:c r="L8" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M8" s="8" t="str"/>
+      <x:c r="M8" s="8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
-        <x:v>scan_barcode_format</x:v>
+        <x:v>barcode_payload_url</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
-        <x:v>Detected barcode format</x:v>
+        <x:v>Payload URL</x:v>
       </x:c>
       <x:c r="D9" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Present only when the exact payload is a safe absolute HTTP/HTTPS URL.</x:v>
       </x:c>
       <x:c r="E9" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F9" s="8" t="str"/>
-      <x:c r="G9" s="8" t="str"/>
-      <x:c r="H9" s="8" t="str"/>
-      <x:c r="I9" s="8" t="str"/>
-      <x:c r="J9" s="8" t="str"/>
-      <x:c r="K9" s="8" t="str"/>
+      <x:c r="F9" s="8"/>
+      <x:c r="G9" s="8" t="str">
+        <x:v>${barcode_payload_kind} = 'url'</x:v>
+      </x:c>
+      <x:c r="H9" s="8"/>
+      <x:c r="I9" s="8"/>
+      <x:c r="J9" s="8"/>
+      <x:c r="K9" s="8"/>
       <x:c r="L9" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M9" s="8" t="str"/>
+      <x:c r="M9" s="8"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>hidden</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
-        <x:v>scan_barcode_payload_kind</x:v>
+        <x:v>barcode_payload_sha256</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
-        <x:v>Payload type</x:v>
+        <x:v>Barcode payload SHA-256</x:v>
       </x:c>
       <x:c r="D10" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E10" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F10" s="8" t="str"/>
-      <x:c r="G10" s="8" t="str"/>
-      <x:c r="H10" s="8" t="str"/>
-      <x:c r="I10" s="8" t="str"/>
-      <x:c r="J10" s="8" t="str"/>
-      <x:c r="K10" s="8" t="str"/>
+        <x:v>SHA-256 of the exact decoded payload.</x:v>
+      </x:c>
+      <x:c r="E10" s="8"/>
+      <x:c r="F10" s="8"/>
+      <x:c r="G10" s="8"/>
+      <x:c r="H10" s="8"/>
+      <x:c r="I10" s="8"/>
+      <x:c r="J10" s="8"/>
+      <x:c r="K10" s="8"/>
       <x:c r="L10" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M10" s="8" t="str"/>
+      <x:c r="M10" s="8"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>hidden</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
-        <x:v>scan_barcode_payload_url</x:v>
+        <x:v>verification_evidence_format</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>Payload URL</x:v>
+        <x:v>Verification evidence format</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E11" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F11" s="8" t="str"/>
-      <x:c r="G11" s="8" t="str"/>
-      <x:c r="H11" s="8" t="str"/>
-      <x:c r="I11" s="8" t="str"/>
-      <x:c r="J11" s="8" t="str"/>
-      <x:c r="K11" s="8" t="str"/>
+        <x:v>Evidence recipe identifier.</x:v>
+      </x:c>
+      <x:c r="E11" s="8"/>
+      <x:c r="F11" s="8"/>
+      <x:c r="G11" s="8"/>
+      <x:c r="H11" s="8"/>
+      <x:c r="I11" s="8"/>
+      <x:c r="J11" s="8"/>
+      <x:c r="K11" s="8"/>
       <x:c r="L11" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M11" s="8" t="str"/>
+      <x:c r="M11" s="8"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>hidden</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
-        <x:v>scan_barcode_scan_time_iso</x:v>
+        <x:v>verification_evidence_hash</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
-        <x:v>Scan time</x:v>
+        <x:v>Verification evidence hash</x:v>
       </x:c>
       <x:c r="D12" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E12" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F12" s="8" t="str"/>
-      <x:c r="G12" s="8" t="str"/>
-      <x:c r="H12" s="8" t="str"/>
-      <x:c r="I12" s="8" t="str"/>
-      <x:c r="J12" s="8" t="str"/>
-      <x:c r="K12" s="8" t="str"/>
+        <x:v>Evidence hash for this payload.</x:v>
+      </x:c>
+      <x:c r="E12" s="8"/>
+      <x:c r="F12" s="8"/>
+      <x:c r="G12" s="8"/>
+      <x:c r="H12" s="8"/>
+      <x:c r="I12" s="8"/>
+      <x:c r="J12" s="8"/>
+      <x:c r="K12" s="8"/>
       <x:c r="L12" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M12" s="8" t="str"/>
+      <x:c r="M12" s="8"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="8" t="str">
         <x:v>text</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
-        <x:v>scan_barcode_source</x:v>
+        <x:v>barcode_scan_time_iso</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
-        <x:v>Capture source</x:v>
+        <x:v>Scan time</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>ISO-8601 capture time.</x:v>
       </x:c>
       <x:c r="E13" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F13" s="8" t="str"/>
-      <x:c r="G13" s="8" t="str"/>
-      <x:c r="H13" s="8" t="str"/>
-      <x:c r="I13" s="8" t="str"/>
-      <x:c r="J13" s="8" t="str"/>
-      <x:c r="K13" s="8" t="str"/>
+      <x:c r="F13" s="8"/>
+      <x:c r="G13" s="8"/>
+      <x:c r="H13" s="8"/>
+      <x:c r="I13" s="8"/>
+      <x:c r="J13" s="8"/>
+      <x:c r="K13" s="8"/>
       <x:c r="L13" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M13" s="8" t="str"/>
+      <x:c r="M13" s="8"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="8" t="str">
-        <x:v>hidden</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
-        <x:v>scan_barcode_payload_sha256</x:v>
+        <x:v>barcode_source</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
-        <x:v>Scan Barcode Payload Sha256</x:v>
+        <x:v>Capture source</x:v>
       </x:c>
       <x:c r="D14" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Scanner/source identifier.</x:v>
       </x:c>
       <x:c r="E14" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F14" s="8" t="str"/>
-      <x:c r="G14" s="8" t="str"/>
-      <x:c r="H14" s="8" t="str"/>
-      <x:c r="I14" s="8" t="str"/>
-      <x:c r="J14" s="8" t="str"/>
-      <x:c r="K14" s="8" t="str"/>
+      <x:c r="F14" s="8"/>
+      <x:c r="G14" s="8"/>
+      <x:c r="H14" s="8"/>
+      <x:c r="I14" s="8"/>
+      <x:c r="J14" s="8"/>
+      <x:c r="K14" s="8"/>
       <x:c r="L14" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M14" s="8" t="str"/>
+      <x:c r="M14" s="8"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="8" t="str">
-        <x:v>hidden</x:v>
+        <x:v>text</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
-        <x:v>scan_verification_evidence_format</x:v>
+        <x:v>methodmesh_full_json</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
-        <x:v>Scan Verification Evidence Format</x:v>
+        <x:v>MethodMesh full JSON</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
+        <x:v>Complete MethodMesh execution/audit payload returned for the handled roundtrip.</x:v>
       </x:c>
       <x:c r="E15" s="8" t="str">
         <x:v>hidden-answer</x:v>
       </x:c>
-      <x:c r="F15" s="8" t="str"/>
-      <x:c r="G15" s="8" t="str"/>
-      <x:c r="H15" s="8" t="str"/>
-      <x:c r="I15" s="8" t="str"/>
-      <x:c r="J15" s="8" t="str"/>
-      <x:c r="K15" s="8" t="str"/>
+      <x:c r="F15" s="8"/>
+      <x:c r="G15" s="8"/>
+      <x:c r="H15" s="8"/>
+      <x:c r="I15" s="8"/>
+      <x:c r="J15" s="8"/>
+      <x:c r="K15" s="8"/>
       <x:c r="L15" s="8" t="str">
         <x:v>yes</x:v>
       </x:c>
-      <x:c r="M15" s="8" t="str"/>
+      <x:c r="M15" s="8"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="8" t="str">
-        <x:v>hidden</x:v>
-      </x:c>
-      <x:c r="B16" s="8" t="str">
-        <x:v>scan_verification_evidence_hash</x:v>
-      </x:c>
-      <x:c r="C16" s="8" t="str">
-        <x:v>Scan Verification Evidence Hash</x:v>
-      </x:c>
-      <x:c r="D16" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E16" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F16" s="8" t="str"/>
-      <x:c r="G16" s="8" t="str"/>
-      <x:c r="H16" s="8" t="str"/>
-      <x:c r="I16" s="8" t="str"/>
-      <x:c r="J16" s="8" t="str"/>
-      <x:c r="K16" s="8" t="str"/>
-      <x:c r="L16" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M16" s="8" t="str"/>
+        <x:v>end_group</x:v>
+      </x:c>
+      <x:c r="B16" s="8"/>
+      <x:c r="C16" s="8"/>
+      <x:c r="D16" s="8"/>
+      <x:c r="E16" s="8"/>
+      <x:c r="F16" s="8"/>
+      <x:c r="G16" s="8"/>
+      <x:c r="H16" s="8"/>
+      <x:c r="I16" s="8"/>
+      <x:c r="J16" s="8"/>
+      <x:c r="K16" s="8"/>
+      <x:c r="L16" s="8"/>
+      <x:c r="M16" s="8"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="8" t="str">
-        <x:v>hidden</x:v>
+        <x:v>note</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
-        <x:v>scan_methodmesh_full_json</x:v>
+        <x:v>return_summary</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
-        <x:v>Scan Methodmesh Full Json</x:v>
+        <x:v>MethodMesh return captured. Status: ${methodmesh_status}</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
-        <x:v>Returned by MethodMesh.</x:v>
-      </x:c>
-      <x:c r="E17" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F17" s="8" t="str"/>
-      <x:c r="G17" s="8" t="str"/>
-      <x:c r="H17" s="8" t="str"/>
-      <x:c r="I17" s="8" t="str"/>
-      <x:c r="J17" s="8" t="str"/>
-      <x:c r="K17" s="8" t="str"/>
-      <x:c r="L17" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M17" s="8" t="str"/>
+        <x:v>Decoded payload: ${barcode_payload}</x:v>
+      </x:c>
+      <x:c r="E17" s="8"/>
+      <x:c r="F17" s="8"/>
+      <x:c r="G17" s="8" t="str">
+        <x:v>${barcode_payload} != ''</x:v>
+      </x:c>
+      <x:c r="H17" s="8"/>
+      <x:c r="I17" s="8"/>
+      <x:c r="J17" s="8"/>
+      <x:c r="K17" s="8"/>
+      <x:c r="L17" s="8"/>
+      <x:c r="M17" s="8"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="8" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="B18" s="8" t="str">
-        <x:v>methodmesh_full_json</x:v>
-      </x:c>
-      <x:c r="C18" s="8" t="str">
-        <x:v>Methodmesh Full Json</x:v>
-      </x:c>
-      <x:c r="D18" s="8" t="str">
-        <x:v>Shared MethodMesh FULL execution envelope. Retained for complete execution/audit capture; capability-specific return fields are projected separately.</x:v>
-      </x:c>
-      <x:c r="E18" s="8" t="str">
-        <x:v>hidden-answer</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="str"/>
-      <x:c r="G18" s="8" t="str"/>
-      <x:c r="H18" s="8" t="str"/>
-      <x:c r="I18" s="8" t="str"/>
-      <x:c r="J18" s="8" t="str"/>
-      <x:c r="K18" s="8" t="str"/>
-      <x:c r="L18" s="8" t="str">
-        <x:v>yes</x:v>
-      </x:c>
-      <x:c r="M18" s="8" t="str"/>
+      <x:c r="A18" s="8"/>
+      <x:c r="B18" s="8"/>
+      <x:c r="C18" s="8"/>
+      <x:c r="D18" s="8"/>
+      <x:c r="E18" s="8"/>
+      <x:c r="F18" s="8"/>
+      <x:c r="G18" s="8"/>
+      <x:c r="H18" s="8"/>
+      <x:c r="I18" s="8"/>
+      <x:c r="J18" s="8"/>
+      <x:c r="K18" s="8"/>
+      <x:c r="L18" s="8"/>
+      <x:c r="M18" s="8"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="8" t="str">
-        <x:v>end_group</x:v>
-      </x:c>
-      <x:c r="B19" s="8" t="str"/>
-      <x:c r="C19" s="8" t="str"/>
-      <x:c r="D19" s="8" t="str"/>
-      <x:c r="E19" s="8" t="str"/>
-      <x:c r="F19" s="8" t="str"/>
-      <x:c r="G19" s="8" t="str"/>
-      <x:c r="H19" s="8" t="str"/>
-      <x:c r="I19" s="8" t="str"/>
-      <x:c r="J19" s="8" t="str"/>
-      <x:c r="K19" s="8" t="str"/>
-      <x:c r="L19" s="8" t="str"/>
-      <x:c r="M19" s="8" t="str"/>
+      <x:c r="A19" s="8"/>
+      <x:c r="B19" s="8"/>
+      <x:c r="C19" s="8"/>
+      <x:c r="D19" s="8"/>
+      <x:c r="E19" s="8"/>
+      <x:c r="F19" s="8"/>
+      <x:c r="G19" s="8"/>
+      <x:c r="H19" s="8"/>
+      <x:c r="I19" s="8"/>
+      <x:c r="J19" s="8"/>
+      <x:c r="K19" s="8"/>
+      <x:c r="L19" s="8"/>
+      <x:c r="M19" s="8"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="8" t="str">
-        <x:v>note</x:v>
-      </x:c>
-      <x:c r="B20" s="8" t="str">
-        <x:v>return_summary</x:v>
-      </x:c>
-      <x:c r="C20" s="8" t="str">
-        <x:v>MethodMesh return captured. Status: ${methodmesh_status}</x:v>
-      </x:c>
-      <x:c r="D20" s="8" t="str">
-        <x:v>Only fields relevant to this capability are stored, plus the shared FULL envelope.</x:v>
-      </x:c>
-      <x:c r="E20" s="8" t="str"/>
-      <x:c r="F20" s="8" t="str"/>
-      <x:c r="G20" s="8" t="str"/>
-      <x:c r="H20" s="8" t="str"/>
-      <x:c r="I20" s="8" t="str"/>
-      <x:c r="J20" s="8" t="str"/>
-      <x:c r="K20" s="8" t="str"/>
-      <x:c r="L20" s="8" t="str"/>
-      <x:c r="M20" s="8" t="str"/>
+      <x:c r="A20" s="8"/>
+      <x:c r="B20" s="8"/>
+      <x:c r="C20" s="8"/>
+      <x:c r="D20" s="8"/>
+      <x:c r="E20" s="8"/>
+      <x:c r="F20" s="8"/>
+      <x:c r="G20" s="8"/>
+      <x:c r="H20" s="8"/>
+      <x:c r="I20" s="8"/>
+      <x:c r="J20" s="8"/>
+      <x:c r="K20" s="8"/>
+      <x:c r="L20" s="8"/>
+      <x:c r="M20" s="8"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -971,6 +935,11 @@
       <x:c r="C1" s="3" t="str">
         <x:v>version</x:v>
       </x:c>
+      <x:c r="D1" t="str">
+        <x:v>instance_name</x:v>
+      </x:c>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -980,8 +949,13 @@
         <x:v>qrcode_barcode_scan</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>2026090701</x:v>
-      </x:c>
+        <x:v>2026091201</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>${barcode_payload}</x:v>
+      </x:c>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
